--- a/Luban/Data/#animationprofile.xlsx
+++ b/Luban/Data/#animationprofile.xlsx
@@ -843,7 +843,7 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>override</t>
+          <t>overlay</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
